--- a/음원_구성표_상세.xlsx
+++ b/음원_구성표_상세.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="음원 구성표" sheetId="1" r:id="R7b52023af6e4447c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연구 근거" sheetId="2" r:id="R73f6b419f6934d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="음원 구성표" sheetId="1" r:id="R974bb0e4d3bb4588"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연구 근거" sheetId="2" r:id="R874c0264b5454e84"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46,7 +46,7 @@
       <x:name val="Noto Sans CJK KR"/>
     </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -113,6 +113,11 @@
         <x:fgColor rgb="FFF2EBF6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9F1F0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -126,7 +131,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -193,6 +198,9 @@
     <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -201,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SoundEvidence" displayName="SoundEvidence" ref="A1:AF196" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:AF196"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SoundEvidence" displayName="SoundEvidence" ref="A1:AF211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:AF211"/>
   <x:tableColumns count="32">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="제목"/>
@@ -10348,7 +10356,7 @@
         <x:v>audio/SN181.mp3</x:v>
       </x:c>
       <x:c r="Q92" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN181.png</x:v>
       </x:c>
       <x:c r="R92" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -10454,7 +10462,7 @@
         <x:v>audio/SN182.mp3</x:v>
       </x:c>
       <x:c r="Q93" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN182.png</x:v>
       </x:c>
       <x:c r="R93" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -10560,7 +10568,7 @@
         <x:v>audio/SN183.mp3</x:v>
       </x:c>
       <x:c r="Q94" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN183.png</x:v>
       </x:c>
       <x:c r="R94" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -10666,7 +10674,7 @@
         <x:v>audio/SN184.mp3</x:v>
       </x:c>
       <x:c r="Q95" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN184.png</x:v>
       </x:c>
       <x:c r="R95" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -10772,7 +10780,7 @@
         <x:v>audio/SN185.mp3</x:v>
       </x:c>
       <x:c r="Q96" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN185.png</x:v>
       </x:c>
       <x:c r="R96" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -10878,7 +10886,7 @@
         <x:v>audio/SN186.mp3</x:v>
       </x:c>
       <x:c r="Q97" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN186.png</x:v>
       </x:c>
       <x:c r="R97" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -10984,7 +10992,7 @@
         <x:v>audio/SN187.mp3</x:v>
       </x:c>
       <x:c r="Q98" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN187.png</x:v>
       </x:c>
       <x:c r="R98" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11090,7 +11098,7 @@
         <x:v>audio/SN188.mp3</x:v>
       </x:c>
       <x:c r="Q99" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN188.png</x:v>
       </x:c>
       <x:c r="R99" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11196,7 +11204,7 @@
         <x:v>audio/SN189.mp3</x:v>
       </x:c>
       <x:c r="Q100" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN189.png</x:v>
       </x:c>
       <x:c r="R100" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11302,7 +11310,7 @@
         <x:v>audio/SN190.mp3</x:v>
       </x:c>
       <x:c r="Q101" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN190.png</x:v>
       </x:c>
       <x:c r="R101" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11408,7 +11416,7 @@
         <x:v>audio/SN191.mp3</x:v>
       </x:c>
       <x:c r="Q102" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN191.png</x:v>
       </x:c>
       <x:c r="R102" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11514,7 +11522,7 @@
         <x:v>audio/SN192.mp3</x:v>
       </x:c>
       <x:c r="Q103" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN192.png</x:v>
       </x:c>
       <x:c r="R103" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11620,7 +11628,7 @@
         <x:v>audio/SN193.mp3</x:v>
       </x:c>
       <x:c r="Q104" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN193.png</x:v>
       </x:c>
       <x:c r="R104" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11726,7 +11734,7 @@
         <x:v>audio/SN194.mp3</x:v>
       </x:c>
       <x:c r="Q105" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN194.png</x:v>
       </x:c>
       <x:c r="R105" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11832,7 +11840,7 @@
         <x:v>audio/SN195.mp3</x:v>
       </x:c>
       <x:c r="Q106" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN195.png</x:v>
       </x:c>
       <x:c r="R106" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -11938,7 +11946,7 @@
         <x:v>audio/SN196.mp3</x:v>
       </x:c>
       <x:c r="Q107" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN196.png</x:v>
       </x:c>
       <x:c r="R107" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12044,7 +12052,7 @@
         <x:v>audio/SN197.mp3</x:v>
       </x:c>
       <x:c r="Q108" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN197.png</x:v>
       </x:c>
       <x:c r="R108" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12150,7 +12158,7 @@
         <x:v>audio/SN198.mp3</x:v>
       </x:c>
       <x:c r="Q109" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN198.png</x:v>
       </x:c>
       <x:c r="R109" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12256,7 +12264,7 @@
         <x:v>audio/SN199.mp3</x:v>
       </x:c>
       <x:c r="Q110" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN199.png</x:v>
       </x:c>
       <x:c r="R110" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12362,7 +12370,7 @@
         <x:v>audio/SN200.mp3</x:v>
       </x:c>
       <x:c r="Q111" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN200.png</x:v>
       </x:c>
       <x:c r="R111" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12468,7 +12476,7 @@
         <x:v>audio/SN201.mp3</x:v>
       </x:c>
       <x:c r="Q112" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN201.png</x:v>
       </x:c>
       <x:c r="R112" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12574,7 +12582,7 @@
         <x:v>audio/SN202.mp3</x:v>
       </x:c>
       <x:c r="Q113" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN202.png</x:v>
       </x:c>
       <x:c r="R113" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12680,7 +12688,7 @@
         <x:v>audio/SN203.mp3</x:v>
       </x:c>
       <x:c r="Q114" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN203.png</x:v>
       </x:c>
       <x:c r="R114" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12786,7 +12794,7 @@
         <x:v>audio/SN204.mp3</x:v>
       </x:c>
       <x:c r="Q115" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN204.png</x:v>
       </x:c>
       <x:c r="R115" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12892,7 +12900,7 @@
         <x:v>audio/SN205.mp3</x:v>
       </x:c>
       <x:c r="Q116" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN205.png</x:v>
       </x:c>
       <x:c r="R116" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -12998,7 +13006,7 @@
         <x:v>audio/SN206.mp3</x:v>
       </x:c>
       <x:c r="Q117" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN206.png</x:v>
       </x:c>
       <x:c r="R117" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -13104,7 +13112,7 @@
         <x:v>audio/SN207.mp3</x:v>
       </x:c>
       <x:c r="Q118" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN207.png</x:v>
       </x:c>
       <x:c r="R118" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -13210,7 +13218,7 @@
         <x:v>audio/SN208.mp3</x:v>
       </x:c>
       <x:c r="Q119" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN208.png</x:v>
       </x:c>
       <x:c r="R119" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -13316,7 +13324,7 @@
         <x:v>audio/SN209.mp3</x:v>
       </x:c>
       <x:c r="Q120" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN209.png</x:v>
       </x:c>
       <x:c r="R120" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -13422,7 +13430,7 @@
         <x:v>audio/SN210.mp3</x:v>
       </x:c>
       <x:c r="Q121" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN210.png</x:v>
       </x:c>
       <x:c r="R121" s="20" t="str">
         <x:v>지속주의</x:v>
@@ -13528,7 +13536,7 @@
         <x:v>audio/SN211.mp3</x:v>
       </x:c>
       <x:c r="Q122" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN211.png</x:v>
       </x:c>
       <x:c r="R122" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -13634,7 +13642,7 @@
         <x:v>audio/SN212.mp3</x:v>
       </x:c>
       <x:c r="Q123" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN212.png</x:v>
       </x:c>
       <x:c r="R123" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -13740,7 +13748,7 @@
         <x:v>audio/SN213.mp3</x:v>
       </x:c>
       <x:c r="Q124" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN213.png</x:v>
       </x:c>
       <x:c r="R124" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -13846,7 +13854,7 @@
         <x:v>audio/SN214.mp3</x:v>
       </x:c>
       <x:c r="Q125" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN214.png</x:v>
       </x:c>
       <x:c r="R125" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -13952,7 +13960,7 @@
         <x:v>audio/SN215.mp3</x:v>
       </x:c>
       <x:c r="Q126" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN215.png</x:v>
       </x:c>
       <x:c r="R126" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14058,7 +14066,7 @@
         <x:v>audio/SN216.mp3</x:v>
       </x:c>
       <x:c r="Q127" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN216.png</x:v>
       </x:c>
       <x:c r="R127" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14164,7 +14172,7 @@
         <x:v>audio/SN217.mp3</x:v>
       </x:c>
       <x:c r="Q128" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN217.png</x:v>
       </x:c>
       <x:c r="R128" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14270,7 +14278,7 @@
         <x:v>audio/SN218.mp3</x:v>
       </x:c>
       <x:c r="Q129" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN218.png</x:v>
       </x:c>
       <x:c r="R129" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14376,7 +14384,7 @@
         <x:v>audio/SN219.mp3</x:v>
       </x:c>
       <x:c r="Q130" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN219.png</x:v>
       </x:c>
       <x:c r="R130" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14482,7 +14490,7 @@
         <x:v>audio/SN220.mp3</x:v>
       </x:c>
       <x:c r="Q131" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN220.png</x:v>
       </x:c>
       <x:c r="R131" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14588,7 +14596,7 @@
         <x:v>audio/SN221.mp3</x:v>
       </x:c>
       <x:c r="Q132" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN221.png</x:v>
       </x:c>
       <x:c r="R132" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14694,7 +14702,7 @@
         <x:v>audio/SN222.mp3</x:v>
       </x:c>
       <x:c r="Q133" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN222.png</x:v>
       </x:c>
       <x:c r="R133" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14800,7 +14808,7 @@
         <x:v>audio/SN223.mp3</x:v>
       </x:c>
       <x:c r="Q134" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN223.png</x:v>
       </x:c>
       <x:c r="R134" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -14906,7 +14914,7 @@
         <x:v>audio/SN224.mp3</x:v>
       </x:c>
       <x:c r="Q135" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN224.png</x:v>
       </x:c>
       <x:c r="R135" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -15012,7 +15020,7 @@
         <x:v>audio/SN225.mp3</x:v>
       </x:c>
       <x:c r="Q136" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN225.png</x:v>
       </x:c>
       <x:c r="R136" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -15118,7 +15126,7 @@
         <x:v>audio/SN226.mp3</x:v>
       </x:c>
       <x:c r="Q137" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN226.png</x:v>
       </x:c>
       <x:c r="R137" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -15224,7 +15232,7 @@
         <x:v>audio/SN227.mp3</x:v>
       </x:c>
       <x:c r="Q138" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN227.png</x:v>
       </x:c>
       <x:c r="R138" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -15330,7 +15338,7 @@
         <x:v>audio/SN228.mp3</x:v>
       </x:c>
       <x:c r="Q139" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN228.png</x:v>
       </x:c>
       <x:c r="R139" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -15436,7 +15444,7 @@
         <x:v>audio/SN229.mp3</x:v>
       </x:c>
       <x:c r="Q140" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN229.png</x:v>
       </x:c>
       <x:c r="R140" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -15542,7 +15550,7 @@
         <x:v>audio/SN230.mp3</x:v>
       </x:c>
       <x:c r="Q141" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN230.png</x:v>
       </x:c>
       <x:c r="R141" s="21" t="str">
         <x:v>지속주의</x:v>
@@ -15648,7 +15656,7 @@
         <x:v>audio/SN231.mp3</x:v>
       </x:c>
       <x:c r="Q142" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN231.png</x:v>
       </x:c>
       <x:c r="R142" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -15754,7 +15762,7 @@
         <x:v>audio/SN232.mp3</x:v>
       </x:c>
       <x:c r="Q143" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN232.png</x:v>
       </x:c>
       <x:c r="R143" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -15860,7 +15868,7 @@
         <x:v>audio/SN233.mp3</x:v>
       </x:c>
       <x:c r="Q144" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN233.png</x:v>
       </x:c>
       <x:c r="R144" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -15966,7 +15974,7 @@
         <x:v>audio/SN234.mp3</x:v>
       </x:c>
       <x:c r="Q145" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN234.png</x:v>
       </x:c>
       <x:c r="R145" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -16072,7 +16080,7 @@
         <x:v>audio/SN235.mp3</x:v>
       </x:c>
       <x:c r="Q146" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN235.png</x:v>
       </x:c>
       <x:c r="R146" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -16178,7 +16186,7 @@
         <x:v>audio/SN236.mp3</x:v>
       </x:c>
       <x:c r="Q147" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN236.png</x:v>
       </x:c>
       <x:c r="R147" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -16284,7 +16292,7 @@
         <x:v>audio/SN237.mp3</x:v>
       </x:c>
       <x:c r="Q148" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN237.png</x:v>
       </x:c>
       <x:c r="R148" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -16390,7 +16398,7 @@
         <x:v>audio/SN238.mp3</x:v>
       </x:c>
       <x:c r="Q149" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN238.png</x:v>
       </x:c>
       <x:c r="R149" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -16496,7 +16504,7 @@
         <x:v>audio/SN239.mp3</x:v>
       </x:c>
       <x:c r="Q150" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN239.png</x:v>
       </x:c>
       <x:c r="R150" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -16602,7 +16610,7 @@
         <x:v>audio/SN240.mp3</x:v>
       </x:c>
       <x:c r="Q151" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN240.png</x:v>
       </x:c>
       <x:c r="R151" s="21" t="str">
         <x:v>청각주의 · 지속주의</x:v>
@@ -16708,7 +16716,7 @@
         <x:v>audio/SN241.mp3</x:v>
       </x:c>
       <x:c r="Q152" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN241.png</x:v>
       </x:c>
       <x:c r="R152" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -16814,7 +16822,7 @@
         <x:v>audio/SN242.mp3</x:v>
       </x:c>
       <x:c r="Q153" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN242.png</x:v>
       </x:c>
       <x:c r="R153" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -16920,7 +16928,7 @@
         <x:v>audio/SN243.mp3</x:v>
       </x:c>
       <x:c r="Q154" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN243.png</x:v>
       </x:c>
       <x:c r="R154" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -17026,7 +17034,7 @@
         <x:v>audio/SN244.mp3</x:v>
       </x:c>
       <x:c r="Q155" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN244.png</x:v>
       </x:c>
       <x:c r="R155" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -17132,7 +17140,7 @@
         <x:v>audio/SN245.mp3</x:v>
       </x:c>
       <x:c r="Q156" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN245.png</x:v>
       </x:c>
       <x:c r="R156" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -17238,7 +17246,7 @@
         <x:v>audio/SN246.mp3</x:v>
       </x:c>
       <x:c r="Q157" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN246.png</x:v>
       </x:c>
       <x:c r="R157" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -17344,7 +17352,7 @@
         <x:v>audio/SN247.mp3</x:v>
       </x:c>
       <x:c r="Q158" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN247.png</x:v>
       </x:c>
       <x:c r="R158" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -17450,7 +17458,7 @@
         <x:v>audio/SN248.mp3</x:v>
       </x:c>
       <x:c r="Q159" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN248.png</x:v>
       </x:c>
       <x:c r="R159" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -17556,7 +17564,7 @@
         <x:v>audio/SN249.mp3</x:v>
       </x:c>
       <x:c r="Q160" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN249.png</x:v>
       </x:c>
       <x:c r="R160" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -17662,7 +17670,7 @@
         <x:v>audio/SN250.mp3</x:v>
       </x:c>
       <x:c r="Q161" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN250.png</x:v>
       </x:c>
       <x:c r="R161" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -17768,7 +17776,7 @@
         <x:v>audio/SN251.mp3</x:v>
       </x:c>
       <x:c r="Q162" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN251.png</x:v>
       </x:c>
       <x:c r="R162" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -17874,7 +17882,7 @@
         <x:v>audio/SN252.mp3</x:v>
       </x:c>
       <x:c r="Q163" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN252.png</x:v>
       </x:c>
       <x:c r="R163" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -17980,7 +17988,7 @@
         <x:v>audio/SN253.mp3</x:v>
       </x:c>
       <x:c r="Q164" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN253.png</x:v>
       </x:c>
       <x:c r="R164" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -18086,7 +18094,7 @@
         <x:v>audio/SN254.mp3</x:v>
       </x:c>
       <x:c r="Q165" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN254.png</x:v>
       </x:c>
       <x:c r="R165" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -18192,7 +18200,7 @@
         <x:v>audio/SN255.mp3</x:v>
       </x:c>
       <x:c r="Q166" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN255.png</x:v>
       </x:c>
       <x:c r="R166" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -18298,7 +18306,7 @@
         <x:v>audio/SN256.mp3</x:v>
       </x:c>
       <x:c r="Q167" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN256.png</x:v>
       </x:c>
       <x:c r="R167" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -18404,7 +18412,7 @@
         <x:v>audio/SN257.mp3</x:v>
       </x:c>
       <x:c r="Q168" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN257.png</x:v>
       </x:c>
       <x:c r="R168" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -18510,7 +18518,7 @@
         <x:v>audio/SN258.mp3</x:v>
       </x:c>
       <x:c r="Q169" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN258.png</x:v>
       </x:c>
       <x:c r="R169" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -18616,7 +18624,7 @@
         <x:v>audio/SN259.mp3</x:v>
       </x:c>
       <x:c r="Q170" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN259.png</x:v>
       </x:c>
       <x:c r="R170" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -18722,7 +18730,7 @@
         <x:v>audio/SN260.mp3</x:v>
       </x:c>
       <x:c r="Q171" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN260.png</x:v>
       </x:c>
       <x:c r="R171" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -18828,7 +18836,7 @@
         <x:v>audio/SN261.mp3</x:v>
       </x:c>
       <x:c r="Q172" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN261.png</x:v>
       </x:c>
       <x:c r="R172" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -18934,7 +18942,7 @@
         <x:v>audio/SN262.mp3</x:v>
       </x:c>
       <x:c r="Q173" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN262.png</x:v>
       </x:c>
       <x:c r="R173" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -19040,7 +19048,7 @@
         <x:v>audio/SN263.mp3</x:v>
       </x:c>
       <x:c r="Q174" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN263.png</x:v>
       </x:c>
       <x:c r="R174" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -19146,7 +19154,7 @@
         <x:v>audio/SN264.mp3</x:v>
       </x:c>
       <x:c r="Q175" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN264.png</x:v>
       </x:c>
       <x:c r="R175" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -19252,7 +19260,7 @@
         <x:v>audio/SN265.mp3</x:v>
       </x:c>
       <x:c r="Q176" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN265.png</x:v>
       </x:c>
       <x:c r="R176" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -19358,7 +19366,7 @@
         <x:v>audio/SN266.mp3</x:v>
       </x:c>
       <x:c r="Q177" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN266.png</x:v>
       </x:c>
       <x:c r="R177" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -19464,7 +19472,7 @@
         <x:v>audio/SN267.mp3</x:v>
       </x:c>
       <x:c r="Q178" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN267.png</x:v>
       </x:c>
       <x:c r="R178" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -19570,7 +19578,7 @@
         <x:v>audio/SN268.mp3</x:v>
       </x:c>
       <x:c r="Q179" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN268.png</x:v>
       </x:c>
       <x:c r="R179" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -19676,7 +19684,7 @@
         <x:v>audio/SN269.mp3</x:v>
       </x:c>
       <x:c r="Q180" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN269.png</x:v>
       </x:c>
       <x:c r="R180" s="22" t="str">
         <x:v>지속주의</x:v>
@@ -19782,7 +19790,7 @@
         <x:v>audio/SN270.mp3</x:v>
       </x:c>
       <x:c r="Q181" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN270.png</x:v>
       </x:c>
       <x:c r="R181" s="22" t="str">
         <x:v>지속주의 · 청각주의</x:v>
@@ -19888,7 +19896,7 @@
         <x:v>audio/SN271.mp3</x:v>
       </x:c>
       <x:c r="Q182" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN271.png</x:v>
       </x:c>
       <x:c r="R182" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -19995,7 +20003,7 @@
         <x:v>audio/SN272.mp3</x:v>
       </x:c>
       <x:c r="Q183" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN272.png</x:v>
       </x:c>
       <x:c r="R183" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20102,7 +20110,7 @@
         <x:v>audio/SN273.mp3</x:v>
       </x:c>
       <x:c r="Q184" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN273.png</x:v>
       </x:c>
       <x:c r="R184" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20209,7 +20217,7 @@
         <x:v>audio/SN274.mp3</x:v>
       </x:c>
       <x:c r="Q185" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN274.png</x:v>
       </x:c>
       <x:c r="R185" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20316,7 +20324,7 @@
         <x:v>audio/SN275.mp3</x:v>
       </x:c>
       <x:c r="Q186" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN275.png</x:v>
       </x:c>
       <x:c r="R186" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20423,7 +20431,7 @@
         <x:v>audio/SN276.mp3</x:v>
       </x:c>
       <x:c r="Q187" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN276.png</x:v>
       </x:c>
       <x:c r="R187" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20530,7 +20538,7 @@
         <x:v>audio/SN277.mp3</x:v>
       </x:c>
       <x:c r="Q188" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN277.png</x:v>
       </x:c>
       <x:c r="R188" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20637,7 +20645,7 @@
         <x:v>audio/SN278.mp3</x:v>
       </x:c>
       <x:c r="Q189" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN278.png</x:v>
       </x:c>
       <x:c r="R189" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20744,7 +20752,7 @@
         <x:v>audio/SN279.mp3</x:v>
       </x:c>
       <x:c r="Q190" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN279.png</x:v>
       </x:c>
       <x:c r="R190" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20851,7 +20859,7 @@
         <x:v>audio/SN280.mp3</x:v>
       </x:c>
       <x:c r="Q191" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN280.png</x:v>
       </x:c>
       <x:c r="R191" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -20958,7 +20966,7 @@
         <x:v>audio/SN281.mp3</x:v>
       </x:c>
       <x:c r="Q192" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN281.png</x:v>
       </x:c>
       <x:c r="R192" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -21065,7 +21073,7 @@
         <x:v>audio/SN282.mp3</x:v>
       </x:c>
       <x:c r="Q193" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN282.png</x:v>
       </x:c>
       <x:c r="R193" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -21172,7 +21180,7 @@
         <x:v>audio/SN283.mp3</x:v>
       </x:c>
       <x:c r="Q194" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN283.png</x:v>
       </x:c>
       <x:c r="R194" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -21279,7 +21287,7 @@
         <x:v>audio/SN284.mp3</x:v>
       </x:c>
       <x:c r="Q195" s="4" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN284.png</x:v>
       </x:c>
       <x:c r="R195" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -21386,7 +21394,7 @@
         <x:v>audio/SN285.mp3</x:v>
       </x:c>
       <x:c r="Q196" s="7" t="str">
-        <x:v>없음(음원 추가분)</x:v>
+        <x:v>images/SN285.png</x:v>
       </x:c>
       <x:c r="R196" s="23" t="str">
         <x:v>지속주의</x:v>
@@ -21443,10 +21451,1600 @@
 [ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
       </x:c>
     </x:row>
+    <x:row r="197" ht="152" customHeight="1">
+      <x:c r="A197" s="10" t="str">
+        <x:v>SN286</x:v>
+      </x:c>
+      <x:c r="B197" s="10" t="str">
+        <x:v>새벽을 두드리는 손</x:v>
+      </x:c>
+      <x:c r="C197" s="4" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D197" s="4" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E197" s="4" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F197" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G197" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H197" s="4" t="str">
+        <x:v>146.83–440</x:v>
+      </x:c>
+      <x:c r="I197" s="4" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J197" s="4" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K197" s="4" t="str">
+        <x:v>145–463</x:v>
+      </x:c>
+      <x:c r="L197" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M197" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N197" s="16" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O197" s="4" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P197" s="4" t="str">
+        <x:v>audio/SN286.mp3</x:v>
+      </x:c>
+      <x:c r="Q197" s="4" t="str">
+        <x:v>images/SN286.png</x:v>
+      </x:c>
+      <x:c r="R197" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S197" s="24" t="str">
+        <x:v>억제·간섭 · 작업기억</x:v>
+      </x:c>
+      <x:c r="T197" s="4" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U197" s="16" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="V197" s="4" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W197" s="4" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X197" s="4" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y197" s="4" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z197" s="4" t="str">
+        <x:v>146.83–440 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA197" s="4" t="str">
+        <x:v>D minor, 4/4. 고른 네 박에 점8분음표 길이의 짧은 응답. 4/4, 4분음표 기준 68 BPM. 가벼운 타이밍·강약 편차. 상행 두드림 뒤 낮은 음으로 돌아오는 여섯 음. 4마디 호흡. 고정 음역 팔레트 50,57,58,60,62,64,65,67,69. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB197" s="4" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC197" s="4" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD197" s="4" t="str">
+        <x:v>선호 기반 과제 진입·유지 배경음 후보. 독해 시 무음 대비 방해 정도 확인.</x:v>
+      </x:c>
+      <x:c r="AE197" s="4" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF197" s="4" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="152" customHeight="1">
+      <x:c r="A198" s="9" t="str">
+        <x:v>SN287</x:v>
+      </x:c>
+      <x:c r="B198" s="9" t="str">
+        <x:v>물방울의 일곱 걸음</x:v>
+      </x:c>
+      <x:c r="C198" s="7" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D198" s="7" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E198" s="7" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F198" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G198" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H198" s="7" t="str">
+        <x:v>164.81–493.88</x:v>
+      </x:c>
+      <x:c r="I198" s="7" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J198" s="7" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K198" s="7" t="str">
+        <x:v>161–587</x:v>
+      </x:c>
+      <x:c r="L198" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M198" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N198" s="15" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O198" s="7" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P198" s="7" t="str">
+        <x:v>audio/SN287.mp3</x:v>
+      </x:c>
+      <x:c r="Q198" s="7" t="str">
+        <x:v>images/SN287.png</x:v>
+      </x:c>
+      <x:c r="R198" s="24" t="str">
+        <x:v>지속주의 · 청각주의</x:v>
+      </x:c>
+      <x:c r="S198" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T198" s="7" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U198" s="15" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="V198" s="7" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W198" s="7" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X198" s="7" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y198" s="7" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z198" s="7" t="str">
+        <x:v>164.81–493.88 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA198" s="7" t="str">
+        <x:v>E minor, 7/8. 2+2+3으로 묶은 일곱 걸음과 마지막 세 박의 여백. 7/8, 4분음표 기준 70 BPM. 가벼운 타이밍·강약 편차. 낮은 물방울과 높은 응답이 교차하는 다섯 음. 3마디 호흡. 고정 음역 팔레트 52,59,60,62,64,66,67,69,71. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB198" s="7" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC198" s="7" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD198" s="7" t="str">
+        <x:v>반복 과제의 유지와 짧은 과제 전환 후보. 주관적 몰입과 정확도 비교.</x:v>
+      </x:c>
+      <x:c r="AE198" s="7" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF198" s="7" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="152" customHeight="1">
+      <x:c r="A199" s="10" t="str">
+        <x:v>SN288</x:v>
+      </x:c>
+      <x:c r="B199" s="10" t="str">
+        <x:v>둥근 바람의 왈츠</x:v>
+      </x:c>
+      <x:c r="C199" s="4" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D199" s="4" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E199" s="4" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F199" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G199" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H199" s="4" t="str">
+        <x:v>174.61–523.25</x:v>
+      </x:c>
+      <x:c r="I199" s="4" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J199" s="4" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K199" s="4" t="str">
+        <x:v>172–560</x:v>
+      </x:c>
+      <x:c r="L199" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M199" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N199" s="16" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O199" s="4" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P199" s="4" t="str">
+        <x:v>audio/SN288.mp3</x:v>
+      </x:c>
+      <x:c r="Q199" s="4" t="str">
+        <x:v>images/SN288.png</x:v>
+      </x:c>
+      <x:c r="R199" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S199" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T199" s="4" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U199" s="16" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="V199" s="4" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W199" s="4" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X199" s="4" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y199" s="4" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z199" s="4" t="str">
+        <x:v>174.61–523.25 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA199" s="4" t="str">
+        <x:v>F major, 3/4. 저음 한 박 뒤 두 번의 가벼운 손끝 응답. 3/4, 4분음표 기준 60 BPM. 가벼운 타이밍·강약 편차. 가운데 음을 감싸며 내려오는 다섯 음 왈츠. 4마디 호흡. 고정 음역 팔레트 53,60,62,64,65,67,69,70,72. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB199" s="4" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC199" s="4" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD199" s="4" t="str">
+        <x:v>선호 기반 과제 진입·유지 배경음 후보. 독해 시 무음 대비 방해 정도 확인.</x:v>
+      </x:c>
+      <x:c r="AE199" s="4" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF199" s="4" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="152" customHeight="1">
+      <x:c r="A200" s="9" t="str">
+        <x:v>SN289</x:v>
+      </x:c>
+      <x:c r="B200" s="9" t="str">
+        <x:v>돌담을 돌아온 박자</x:v>
+      </x:c>
+      <x:c r="C200" s="7" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D200" s="7" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E200" s="7" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F200" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G200" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H200" s="7" t="str">
+        <x:v>110–329.63</x:v>
+      </x:c>
+      <x:c r="I200" s="7" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J200" s="7" t="str">
+        <x:v>저역 중심</x:v>
+      </x:c>
+      <x:c r="K200" s="7" t="str">
+        <x:v>108–334</x:v>
+      </x:c>
+      <x:c r="L200" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M200" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N200" s="15" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O200" s="7" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P200" s="7" t="str">
+        <x:v>audio/SN289.mp3</x:v>
+      </x:c>
+      <x:c r="Q200" s="7" t="str">
+        <x:v>images/SN289.png</x:v>
+      </x:c>
+      <x:c r="R200" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S200" s="24" t="str">
+        <x:v>억제·간섭 · 작업기억</x:v>
+      </x:c>
+      <x:c r="T200" s="7" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U200" s="15" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="V200" s="7" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W200" s="7" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X200" s="7" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y200" s="7" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z200" s="7" t="str">
+        <x:v>110–329.63 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA200" s="7" t="str">
+        <x:v>A minor, 4/4. 두 마디마다 끝 타격을 생략하는 걸음형 박자. 4/4, 4분음표 기준 76 BPM. 가벼운 타이밍·강약 편차. 낮은 두 음으로 출발해 위쪽 음역으로 건너가는 여섯 음. 4마디 호흡. 고정 음역 팔레트 45,52,53,55,57,59,60,62,64. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB200" s="7" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC200" s="7" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD200" s="7" t="str">
+        <x:v>반복 과제의 유지와 짧은 과제 전환 후보. 주관적 몰입과 정확도 비교.</x:v>
+      </x:c>
+      <x:c r="AE200" s="7" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF200" s="7" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="152" customHeight="1">
+      <x:c r="A201" s="10" t="str">
+        <x:v>SN290</x:v>
+      </x:c>
+      <x:c r="B201" s="10" t="str">
+        <x:v>달빛 아래 두 갈래</x:v>
+      </x:c>
+      <x:c r="C201" s="4" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D201" s="4" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E201" s="4" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F201" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G201" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H201" s="4" t="str">
+        <x:v>146.83–440</x:v>
+      </x:c>
+      <x:c r="I201" s="4" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J201" s="4" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K201" s="4" t="str">
+        <x:v>145–522</x:v>
+      </x:c>
+      <x:c r="L201" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M201" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N201" s="16" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O201" s="4" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P201" s="4" t="str">
+        <x:v>audio/SN290.mp3</x:v>
+      </x:c>
+      <x:c r="Q201" s="4" t="str">
+        <x:v>images/SN290.png</x:v>
+      </x:c>
+      <x:c r="R201" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S201" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T201" s="4" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U201" s="16" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="V201" s="4" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W201" s="4" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X201" s="4" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y201" s="4" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z201" s="4" t="str">
+        <x:v>146.83–440 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA201" s="4" t="str">
+        <x:v>D dorian, 6/8. 3+3의 완만한 복합박에 낮은 뮤트 응답. 6/8, 4분음표 기준 56 BPM. 가벼운 타이밍·강약 편차. 서로 다른 음역의 두 갈래를 번갈아 잇는 선율. 3마디 호흡. 고정 음역 팔레트 50,57,59,60,62,64,65,67,69. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB201" s="4" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC201" s="4" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD201" s="4" t="str">
+        <x:v>선호 기반 과제 진입·유지 배경음 후보. 독해 시 무음 대비 방해 정도 확인.</x:v>
+      </x:c>
+      <x:c r="AE201" s="4" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF201" s="4" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="152" customHeight="1">
+      <x:c r="A202" s="9" t="str">
+        <x:v>SN291</x:v>
+      </x:c>
+      <x:c r="B202" s="9" t="str">
+        <x:v>느린 나선의 중심</x:v>
+      </x:c>
+      <x:c r="C202" s="7" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D202" s="7" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E202" s="7" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F202" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G202" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H202" s="7" t="str">
+        <x:v>196–587.33</x:v>
+      </x:c>
+      <x:c r="I202" s="7" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J202" s="7" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K202" s="7" t="str">
+        <x:v>194–624</x:v>
+      </x:c>
+      <x:c r="L202" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M202" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N202" s="15" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O202" s="7" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P202" s="7" t="str">
+        <x:v>audio/SN291.mp3</x:v>
+      </x:c>
+      <x:c r="Q202" s="7" t="str">
+        <x:v>images/SN291.png</x:v>
+      </x:c>
+      <x:c r="R202" s="24" t="str">
+        <x:v>지속주의 · 청각주의</x:v>
+      </x:c>
+      <x:c r="S202" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T202" s="7" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U202" s="15" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="V202" s="7" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W202" s="7" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X202" s="7" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y202" s="7" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z202" s="7" t="str">
+        <x:v>196–587.33 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA202" s="7" t="str">
+        <x:v>G minor, 5/4. 다섯 박을 3+2로 묶고 세 번째 박 뒤에 쉼. 5/4, 4분음표 기준 66 BPM. 가벼운 타이밍·강약 편차. 중심음 주위로 넓어졌다가 닫히는 일곱 음 나선. 5마디 호흡. 고정 음역 팔레트 55,62,63,65,67,69,70,72,74. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB202" s="7" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC202" s="7" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD202" s="7" t="str">
+        <x:v>반복 과제의 유지와 짧은 과제 전환 후보. 주관적 몰입과 정확도 비교.</x:v>
+      </x:c>
+      <x:c r="AE202" s="7" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF202" s="7" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="152" customHeight="1">
+      <x:c r="A203" s="10" t="str">
+        <x:v>SN292</x:v>
+      </x:c>
+      <x:c r="B203" s="10" t="str">
+        <x:v>모래 위의 엇박</x:v>
+      </x:c>
+      <x:c r="C203" s="4" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D203" s="4" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E203" s="4" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F203" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G203" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H203" s="4" t="str">
+        <x:v>110–329.63</x:v>
+      </x:c>
+      <x:c r="I203" s="4" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J203" s="4" t="str">
+        <x:v>저역 중심</x:v>
+      </x:c>
+      <x:c r="K203" s="4" t="str">
+        <x:v>108–345</x:v>
+      </x:c>
+      <x:c r="L203" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M203" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N203" s="16" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O203" s="4" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P203" s="4" t="str">
+        <x:v>audio/SN292.mp3</x:v>
+      </x:c>
+      <x:c r="Q203" s="4" t="str">
+        <x:v>images/SN292.png</x:v>
+      </x:c>
+      <x:c r="R203" s="24" t="str">
+        <x:v>지속주의 · 청각주의</x:v>
+      </x:c>
+      <x:c r="S203" s="24" t="str">
+        <x:v>억제·간섭 · 작업기억</x:v>
+      </x:c>
+      <x:c r="T203" s="4" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U203" s="16" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="V203" s="4" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W203" s="4" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X203" s="4" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y203" s="4" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z203" s="4" t="str">
+        <x:v>110–329.63 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA203" s="4" t="str">
+        <x:v>A minor, 4/4. 4/4 안의 3+3+2 악센트와 뒤박 선율. 4/4, 4분음표 기준 82 BPM. 가벼운 타이밍·강약 편차. 짧은 비약과 낮은 복귀가 교차하는 여섯 음. 4마디 호흡. 고정 음역 팔레트 45,52,53,55,57,59,60,62,64. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB203" s="4" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC203" s="4" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD203" s="4" t="str">
+        <x:v>선호 기반 과제 진입·유지 배경음 후보. 독해 시 무음 대비 방해 정도 확인.</x:v>
+      </x:c>
+      <x:c r="AE203" s="4" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF203" s="4" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="152" customHeight="1">
+      <x:c r="A204" s="9" t="str">
+        <x:v>SN293</x:v>
+      </x:c>
+      <x:c r="B204" s="9" t="str">
+        <x:v>나뭇잎 사이의 응답</x:v>
+      </x:c>
+      <x:c r="C204" s="7" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D204" s="7" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E204" s="7" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F204" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G204" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H204" s="7" t="str">
+        <x:v>164.81–493.88</x:v>
+      </x:c>
+      <x:c r="I204" s="7" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J204" s="7" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K204" s="7" t="str">
+        <x:v>167–560</x:v>
+      </x:c>
+      <x:c r="L204" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M204" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N204" s="15" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O204" s="7" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P204" s="7" t="str">
+        <x:v>audio/SN293.mp3</x:v>
+      </x:c>
+      <x:c r="Q204" s="7" t="str">
+        <x:v>images/SN293.png</x:v>
+      </x:c>
+      <x:c r="R204" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S204" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T204" s="7" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U204" s="15" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="V204" s="7" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W204" s="7" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X204" s="7" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y204" s="7" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z204" s="7" t="str">
+        <x:v>164.81–493.88 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA204" s="7" t="str">
+        <x:v>E dorian, 3/4. 질문 마디와 응답 마디의 악센트를 교대하는 세 박. 3/4, 4분음표 기준 64 BPM. 가벼운 타이밍·강약 편차. 세 음 질문 뒤 세 음 응답으로 이어지는 호흡. 4마디 호흡. 고정 음역 팔레트 52,59,61,62,64,66,67,69,71. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB204" s="7" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC204" s="7" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD204" s="7" t="str">
+        <x:v>반복 과제의 유지와 짧은 과제 전환 후보. 주관적 몰입과 정확도 비교.</x:v>
+      </x:c>
+      <x:c r="AE204" s="7" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF204" s="7" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="152" customHeight="1">
+      <x:c r="A205" s="10" t="str">
+        <x:v>SN294</x:v>
+      </x:c>
+      <x:c r="B205" s="10" t="str">
+        <x:v>작은 파동의 계단</x:v>
+      </x:c>
+      <x:c r="C205" s="4" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D205" s="4" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E205" s="4" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F205" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G205" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H205" s="4" t="str">
+        <x:v>130.81–392</x:v>
+      </x:c>
+      <x:c r="I205" s="4" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J205" s="4" t="str">
+        <x:v>저역 중심</x:v>
+      </x:c>
+      <x:c r="K205" s="4" t="str">
+        <x:v>129–393</x:v>
+      </x:c>
+      <x:c r="L205" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M205" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N205" s="16" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O205" s="4" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P205" s="4" t="str">
+        <x:v>audio/SN294.mp3</x:v>
+      </x:c>
+      <x:c r="Q205" s="4" t="str">
+        <x:v>images/SN294.png</x:v>
+      </x:c>
+      <x:c r="R205" s="24" t="str">
+        <x:v>지속주의 · 청각주의</x:v>
+      </x:c>
+      <x:c r="S205" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T205" s="4" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U205" s="16" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="V205" s="4" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W205" s="4" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X205" s="4" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y205" s="4" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z205" s="4" t="str">
+        <x:v>130.81–392 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA205" s="4" t="str">
+        <x:v>C major, 5/4. 2+3의 다섯 박과 높이가 다른 짧은 뮤트 계단. 5/4, 4분음표 기준 74 BPM. 가벼운 타이밍·강약 편차. 한 음씩 올라가다 두 칸 내려오는 계단형 주제. 5마디 호흡. 고정 음역 팔레트 48,55,57,59,60,62,64,65,67. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB205" s="4" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC205" s="4" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD205" s="4" t="str">
+        <x:v>선호 기반 과제 진입·유지 배경음 후보. 독해 시 무음 대비 방해 정도 확인.</x:v>
+      </x:c>
+      <x:c r="AE205" s="4" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF205" s="4" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="152" customHeight="1">
+      <x:c r="A206" s="9" t="str">
+        <x:v>SN295</x:v>
+      </x:c>
+      <x:c r="B206" s="9" t="str">
+        <x:v>구름을 잇는 여덟 점</x:v>
+      </x:c>
+      <x:c r="C206" s="7" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D206" s="7" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E206" s="7" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F206" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G206" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H206" s="7" t="str">
+        <x:v>174.61–523.25</x:v>
+      </x:c>
+      <x:c r="I206" s="7" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J206" s="7" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K206" s="7" t="str">
+        <x:v>172–657</x:v>
+      </x:c>
+      <x:c r="L206" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M206" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N206" s="15" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O206" s="7" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P206" s="7" t="str">
+        <x:v>audio/SN295.mp3</x:v>
+      </x:c>
+      <x:c r="Q206" s="7" t="str">
+        <x:v>images/SN295.png</x:v>
+      </x:c>
+      <x:c r="R206" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S206" s="24" t="str">
+        <x:v>억제·간섭 · 작업기억</x:v>
+      </x:c>
+      <x:c r="T206" s="7" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U206" s="15" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="V206" s="7" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W206" s="7" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X206" s="7" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y206" s="7" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z206" s="7" t="str">
+        <x:v>174.61–523.25 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA206" s="7" t="str">
+        <x:v>F major, 4/4. 여덟 칸 중 마지막 한 칸을 비우는 고른 8분음표 흐름. 4/4, 4분음표 기준 72 BPM. 가벼운 타이밍·강약 편차. 서로 짝을 이루는 낮은 음과 높은 음의 연결. 4마디 호흡. 고정 음역 팔레트 53,60,62,64,65,67,69,70,72. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB206" s="7" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC206" s="7" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD206" s="7" t="str">
+        <x:v>반복 과제의 유지와 짧은 과제 전환 후보. 주관적 몰입과 정확도 비교.</x:v>
+      </x:c>
+      <x:c r="AE206" s="7" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF206" s="7" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="152" customHeight="1">
+      <x:c r="A207" s="10" t="str">
+        <x:v>SN296</x:v>
+      </x:c>
+      <x:c r="B207" s="10" t="str">
+        <x:v>고요 속 세 번의 울림</x:v>
+      </x:c>
+      <x:c r="C207" s="4" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D207" s="4" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E207" s="4" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F207" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G207" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H207" s="4" t="str">
+        <x:v>146.83–440</x:v>
+      </x:c>
+      <x:c r="I207" s="4" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J207" s="4" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K207" s="4" t="str">
+        <x:v>145–522</x:v>
+      </x:c>
+      <x:c r="L207" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M207" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N207" s="16" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O207" s="4" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P207" s="4" t="str">
+        <x:v>audio/SN296.mp3</x:v>
+      </x:c>
+      <x:c r="Q207" s="4" t="str">
+        <x:v>images/SN296.png</x:v>
+      </x:c>
+      <x:c r="R207" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S207" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T207" s="4" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U207" s="16" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="V207" s="4" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W207" s="4" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X207" s="4" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y207" s="4" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z207" s="4" t="str">
+        <x:v>146.83–440 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA207" s="4" t="str">
+        <x:v>D minor, 3/4. 느린 세 박의 각 머리와 뒤에 부드러운 이중 타격. 3/4, 4분음표 기준 52 BPM. 가벼운 타이밍·강약 편차. 세 묶음의 두 음이 넓은 간격으로 울리는 주제. 3마디 호흡. 고정 음역 팔레트 50,57,58,60,62,64,65,67,69. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB207" s="4" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC207" s="4" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD207" s="4" t="str">
+        <x:v>선호 기반 과제 진입·유지 배경음 후보. 독해 시 무음 대비 방해 정도 확인.</x:v>
+      </x:c>
+      <x:c r="AE207" s="4" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF207" s="4" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="152" customHeight="1">
+      <x:c r="A208" s="9" t="str">
+        <x:v>SN297</x:v>
+      </x:c>
+      <x:c r="B208" s="9" t="str">
+        <x:v>청록의 바깥 궤도</x:v>
+      </x:c>
+      <x:c r="C208" s="7" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D208" s="7" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E208" s="7" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F208" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G208" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H208" s="7" t="str">
+        <x:v>196–587.33</x:v>
+      </x:c>
+      <x:c r="I208" s="7" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J208" s="7" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K208" s="7" t="str">
+        <x:v>194–662</x:v>
+      </x:c>
+      <x:c r="L208" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M208" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N208" s="15" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O208" s="7" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P208" s="7" t="str">
+        <x:v>audio/SN297.mp3</x:v>
+      </x:c>
+      <x:c r="Q208" s="7" t="str">
+        <x:v>images/SN297.png</x:v>
+      </x:c>
+      <x:c r="R208" s="24" t="str">
+        <x:v>지속주의 · 청각주의</x:v>
+      </x:c>
+      <x:c r="S208" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T208" s="7" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U208" s="15" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="V208" s="7" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W208" s="7" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X208" s="7" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y208" s="7" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z208" s="7" t="str">
+        <x:v>196–587.33 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA208" s="7" t="str">
+        <x:v>G dorian, 7/8. 3+2+2 묶음과 중앙 딩이 두 마디마다 돌아오는 일곱 박. 7/8, 4분음표 기준 88 BPM. 가벼운 타이밍·강약 편차. 바깥 음역에서 안쪽으로 접어드는 다섯 음 궤도. 4마디 호흡. 고정 음역 팔레트 55,62,64,65,67,69,70,72,74. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB208" s="7" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC208" s="7" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD208" s="7" t="str">
+        <x:v>반복 과제의 유지와 짧은 과제 전환 후보. 주관적 몰입과 정확도 비교.</x:v>
+      </x:c>
+      <x:c r="AE208" s="7" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF208" s="7" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="152" customHeight="1">
+      <x:c r="A209" s="10" t="str">
+        <x:v>SN298</x:v>
+      </x:c>
+      <x:c r="B209" s="10" t="str">
+        <x:v>비 개인 마당의 리듬</x:v>
+      </x:c>
+      <x:c r="C209" s="4" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D209" s="4" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E209" s="4" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F209" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G209" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H209" s="4" t="str">
+        <x:v>110–329.63</x:v>
+      </x:c>
+      <x:c r="I209" s="4" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J209" s="4" t="str">
+        <x:v>저역 중심</x:v>
+      </x:c>
+      <x:c r="K209" s="4" t="str">
+        <x:v>108–350</x:v>
+      </x:c>
+      <x:c r="L209" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M209" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N209" s="16" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O209" s="4" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P209" s="4" t="str">
+        <x:v>audio/SN298.mp3</x:v>
+      </x:c>
+      <x:c r="Q209" s="4" t="str">
+        <x:v>images/SN298.png</x:v>
+      </x:c>
+      <x:c r="R209" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S209" s="24" t="str">
+        <x:v>억제·간섭 · 작업기억</x:v>
+      </x:c>
+      <x:c r="T209" s="4" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U209" s="16" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="V209" s="4" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W209" s="4" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X209" s="4" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y209" s="4" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z209" s="4" t="str">
+        <x:v>110–329.63 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA209" s="4" t="str">
+        <x:v>A minor, 6/8. 빠르지만 작은 소리의 3+3 구름형 흐름과 마지막 반박 쉼. 6/8, 4분음표 기준 92 BPM. 가벼운 타이밍·강약 편차. 낮은 음에서 밝은 윗음으로 튀었다가 내려오는 다섯 음. 4마디 호흡. 고정 음역 팔레트 45,52,53,55,57,59,60,62,64. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB209" s="4" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC209" s="4" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD209" s="4" t="str">
+        <x:v>선호 기반 과제 진입·유지 배경음 후보. 독해 시 무음 대비 방해 정도 확인.</x:v>
+      </x:c>
+      <x:c r="AE209" s="4" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF209" s="4" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="152" customHeight="1">
+      <x:c r="A210" s="9" t="str">
+        <x:v>SN299</x:v>
+      </x:c>
+      <x:c r="B210" s="9" t="str">
+        <x:v>수평선에 남은 다섯 음</x:v>
+      </x:c>
+      <x:c r="C210" s="7" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D210" s="7" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E210" s="7" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F210" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G210" s="7" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H210" s="7" t="str">
+        <x:v>174.61–523.25</x:v>
+      </x:c>
+      <x:c r="I210" s="7" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J210" s="7" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K210" s="7" t="str">
+        <x:v>172–587</x:v>
+      </x:c>
+      <x:c r="L210" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M210" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N210" s="15" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O210" s="7" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P210" s="7" t="str">
+        <x:v>audio/SN299.mp3</x:v>
+      </x:c>
+      <x:c r="Q210" s="7" t="str">
+        <x:v>images/SN299.png</x:v>
+      </x:c>
+      <x:c r="R210" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S210" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T210" s="7" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U210" s="15" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="V210" s="7" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W210" s="7" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X210" s="7" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y210" s="7" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z210" s="7" t="str">
+        <x:v>174.61–523.25 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA210" s="7" t="str">
+        <x:v>F major, 5/4. 2+1+2의 다섯 박과 중앙 한 박의 숨. 5/4, 4분음표 기준 58 BPM. 가벼운 타이밍·강약 편차. F–G–A–C–D의 다섯 음으로 넓게 오르내리는 선율. 5마디 호흡. 고정 음역 팔레트 53,60,62,64,65,67,69,70,72. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB210" s="7" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC210" s="7" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD210" s="7" t="str">
+        <x:v>반복 과제의 유지와 짧은 과제 전환 후보. 주관적 몰입과 정확도 비교.</x:v>
+      </x:c>
+      <x:c r="AE210" s="7" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF210" s="7" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="152" customHeight="1">
+      <x:c r="A211" s="10" t="str">
+        <x:v>SN300</x:v>
+      </x:c>
+      <x:c r="B211" s="10" t="str">
+        <x:v>처음으로 돌아오는 빛</x:v>
+      </x:c>
+      <x:c r="C211" s="4" t="str">
+        <x:v>핸드팬 모달 합성</x:v>
+      </x:c>
+      <x:c r="D211" s="4" t="str">
+        <x:v>공명 타격·뮤트 타격·몸체 탭 합성. 자연음·ASMR 녹음 미사용.</x:v>
+      </x:c>
+      <x:c r="E211" s="4" t="str">
+        <x:v>악기별 고정 좌우 배치 + 스테레오 잔향. 자동 순환 패닝 없음</x:v>
+      </x:c>
+      <x:c r="F211" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="G211" s="4" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H211" s="4" t="str">
+        <x:v>146.83–440</x:v>
+      </x:c>
+      <x:c r="I211" s="4" t="str">
+        <x:v>없음(타격 음높이로 선율·화성 구성)</x:v>
+      </x:c>
+      <x:c r="J211" s="4" t="str">
+        <x:v>중역 중심</x:v>
+      </x:c>
+      <x:c r="K211" s="4" t="str">
+        <x:v>145–441</x:v>
+      </x:c>
+      <x:c r="L211" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M211" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N211" s="16" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="O211" s="4" t="str">
+        <x:v>MUSIC01, MUSIC02, ACO02, ATT01, ATT02</x:v>
+      </x:c>
+      <x:c r="P211" s="4" t="str">
+        <x:v>audio/SN300.mp3</x:v>
+      </x:c>
+      <x:c r="Q211" s="4" t="str">
+        <x:v>images/SN300.png</x:v>
+      </x:c>
+      <x:c r="R211" s="24" t="str">
+        <x:v>지속주의</x:v>
+      </x:c>
+      <x:c r="S211" s="24" t="str">
+        <x:v>억제·간섭 · 과제 복귀</x:v>
+      </x:c>
+      <x:c r="T211" s="4" t="str">
+        <x:v>추가 핸드팬 15곡</x:v>
+      </x:c>
+      <x:c r="U211" s="16" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="V211" s="4" t="str">
+        <x:v>선호 배경음악과 시간 구조 연구의 유사 근거. 핸드팬 장르의 집중 효과를 직접 입증한 연구는 아님
+[MUSIC01] Kiss &amp; Linnell (2021) https://doi.org/10.1007/s00426-020-01400-6
+[MUSIC02] Bernardi 외 (2006) https://doi.org/10.1136/hrt.2005.064600</x:v>
+      </x:c>
+      <x:c r="W211" s="4" t="str">
+        <x:v>자연음·ASMR 미사용. 실제 구성인 금속 타격·공명은 HANG 악기 음향 연구로 연결
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="X211" s="4" t="str">
+        <x:v>별도 배경층·배경 필터 없음. 음 영역의 진동·결합에 따른 공명 구성 참고
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Y211" s="4" t="str">
+        <x:v>별도 질감층 필터 없음. 타격·뮤트·몸체 탭의 음색 차이를 모달 합성으로 구현
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="Z211" s="4" t="str">
+        <x:v>146.83–440 Hz는 유음 타격의 기음 설정. 주요 부분음·공명 모드를 참고한 합성값이며 주파수별 효능 근거는 아님
+[ACO02] Rossing 외 (2007) https://www.hangblog.org/panart/2-S2-4-IsmaRossing.pdf</x:v>
+      </x:c>
+      <x:c r="AA211" s="4" t="str">
+        <x:v>D major, 4/4. 정박 저음과 조금 늦은 상성부 타격이 만나는 네 박. 4/4, 4분음표 기준 70 BPM. 가벼운 타이밍·강약 편차. 처음 두 음이 종결에서 다시 나타나는 원형 주제. 4마디 호흡. 고정 음역 팔레트 50,57,59,61,62,64,66,67,69. 강화·보완은 해당 구조를 활용한 설계 목표.</x:v>
+      </x:c>
+      <x:c r="AB211" s="4" t="str">
+        <x:v>선호 음악에서 자기보고 과제 집중 증가, 객관적 반응시간 개선 없음 [MUSIC01]. 음악 템포·휴지에 따른 심혈관·호흡 변화 [MUSIC02]. HANG의 부분음·진동 모드 관찰 [ACO02].</x:v>
+      </x:c>
+      <x:c r="AC211" s="4" t="str">
+        <x:v>실제 악기 음향과 일반 배경음악 연구를 참고한 180초 합성 음원. 본 트랙·중학생의 집중력 또는 학업 성과를 직접 검증하지 않음. BPM·Hz·타격 간격·잔향은 제작 설정.</x:v>
+      </x:c>
+      <x:c r="AD211" s="4" t="str">
+        <x:v>선호 기반 과제 진입·유지 배경음 후보. 독해 시 무음 대비 방해 정도 확인.</x:v>
+      </x:c>
+      <x:c r="AE211" s="4" t="str">
+        <x:v>지속주의 누락률·반응시간 변동성 / 읽기 정확도 / 주관적 집중·선호도 / 무음 대비 과제 수행</x:v>
+      </x:c>
+      <x:c r="AF211" s="4" t="str">
+        <x:v>자동 이동 미사용. 목표 위치의 연속성과 선택주의 연구를 참고해 음원 위치 고정. 읽기 간섭은 무음과 비교. 특정 뇌 부위 자극을 뜻하지 않음
+[ATT01] Best 외 (2008) https://doi.org/10.1073/pnas.0803718105
+[ATT02] Vasilev 외 (2018) https://doi.org/10.1177/1745691617747398</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6395d0628eac47b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79395d9aeeb47b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21472,7 +23070,7 @@
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="A1" s="17" t="str">
-        <x:v>SIG-NAPSE | 195곡 근거 검토</x:v>
+        <x:v>SIG-NAPSE | 210곡 근거 검토</x:v>
       </x:c>
       <x:c r="B1" s="17"/>
       <x:c r="C1" s="17"/>
@@ -21528,7 +23126,7 @@
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="18" t="str">
-        <x:v>자료 처리: 기존 90곡·32열·19개 문헌 유지. 로파이 30곡·게임 감성 앰비언트 30곡·미니멀 피아노 30곡·싱잉볼 15곡 추가. 새 음원은 각 180초. 에너지 대역은 완성 음원 측정값이며 이미지는 추가하지 않았습니다.</x:v>
+        <x:v>자료 처리: 기존 195곡·32열·19개 문헌 유지. 핸드팬 15곡(각 180초)과 커버 추가. 에너지 대역은 완성 음원 측정값이며 음원·이미지는 같은 ID로 연결됩니다.</x:v>
       </x:c>
       <x:c r="B5" s="18"/>
       <x:c r="C5" s="18"/>
@@ -22202,7 +23800,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa8096d168fe4d6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48a08c9d32f74ea1"/>
   </x:tableParts>
 </x:worksheet>
 </file>